--- a/www/download/IND.value.m.mv.rpPE.xlsx
+++ b/www/download/IND.value.m.mv.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.092</t>
+          <t>3092097.51794856</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.894</t>
+          <t>2893940.49201627</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.908</t>
+          <t>2908032.83571635</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3.438</t>
+          <t>3437890.39043318</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>3629664.71266894</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.913</t>
+          <t>3912923.12562945</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.112</t>
+          <t>4111948.7658552</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.852</t>
+          <t>3851671.89478015</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.902</t>
+          <t>2902379.05361064</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2.777</t>
+          <t>2776954.57122267</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2.511</t>
+          <t>2511123.00167512</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2.365</t>
+          <t>2365444.10641915</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1969865.70614899</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.801</t>
+          <t>1801133.16201298</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.902</t>
+          <t>1902121.07302464</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.256</t>
+          <t>3255720.29219687</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.432</t>
+          <t>3432042.36325498</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.576</t>
+          <t>3576459.8381327</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3.798</t>
+          <t>3798338.16701662</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4.074</t>
+          <t>4074114.10743038</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.752</t>
+          <t>4752345.30906721</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.788</t>
+          <t>4788049.99812618</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.384</t>
+          <t>4384129.07440858</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3.367</t>
+          <t>3366828.54929775</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3270282.83325573</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>3039842.93614892</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2.867</t>
+          <t>2867399.88983422</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2.342</t>
+          <t>2342413.35607585</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1790170.91186073</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.825</t>
+          <t>1825014.06823097</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.464</t>
+          <t>2464123.1408656</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.439</t>
+          <t>2438682.9464964</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2.578</t>
+          <t>2577704.02877681</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.705</t>
+          <t>2704652.34307228</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2.948</t>
+          <t>2948210.61531722</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3379853.90121113</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.378</t>
+          <t>3377860.15671092</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.173</t>
+          <t>3173039.68445041</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2.618</t>
+          <t>2618090.28726076</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2.555</t>
+          <t>2554945.7161702</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2.415</t>
+          <t>2415425.00786841</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2.261</t>
+          <t>2260980.24598999</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.915</t>
+          <t>1915127.45228249</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>1.905</t>
+          <t>1904565.06118265</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.788</t>
+          <t>1788227.47205863</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>22.793</t>
+          <t>22792975.8905785</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21.209</t>
+          <t>21208782.8496654</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.22</t>
+          <t>23219880.3784247</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>20.129</t>
+          <t>20128980.7790588</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>19.982</t>
+          <t>19981665.1632152</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>18.08</t>
+          <t>18079706.2068398</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15.872</t>
+          <t>15871755.213045</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>13.692</t>
+          <t>13692328.2951084</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>10.317</t>
+          <t>10316974.7892379</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>9.352</t>
+          <t>9352390.43254261</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>8.496</t>
+          <t>8495872.25052271</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7.822</t>
+          <t>7821659.07183965</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>6.064</t>
+          <t>6064161.81890492</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>5.234</t>
+          <t>5233632.33317802</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>5.486</t>
+          <t>5486394.82745046</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>8629641.76164626</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.177</t>
+          <t>8176750.51650779</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>8.097</t>
+          <t>8097069.39202821</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>8.783</t>
+          <t>8783319.76689018</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.004</t>
+          <t>13003841.2033894</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>12.355</t>
+          <t>12354955.9267988</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>14.337</t>
+          <t>14336949.8405138</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.508</t>
+          <t>15507592.7360672</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13.611</t>
+          <t>13610788.9885046</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>12.681</t>
+          <t>12680559.5529093</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10310144.2157772</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>8.748</t>
+          <t>8748141.46205845</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>7.046</t>
+          <t>7045582.6441584</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>5.922</t>
+          <t>5921542.52194117</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>6.346</t>
+          <t>6345837.49692784</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.107</t>
+          <t>4106869.58337966</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.917</t>
+          <t>3916900.24278559</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3820367.54753815</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4.235</t>
+          <t>4234858.6887512</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4230247.13619096</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.236</t>
+          <t>4236440.6298748</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.459</t>
+          <t>4459346.6162948</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.125</t>
+          <t>4124989.09077469</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3.368</t>
+          <t>3368489.11652188</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3.339</t>
+          <t>3339297.81619761</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3.074</t>
+          <t>3073911.77065466</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2.773</t>
+          <t>2772828.04935403</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2.328</t>
+          <t>2328089.71502247</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2.127</t>
+          <t>2126890.69875404</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2.249</t>
+          <t>2249384.02283822</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>49.805</t>
+          <t>49805478.6716984</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>43689864.7047256</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39.683</t>
+          <t>39682793.2398126</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>38.574</t>
+          <t>38573759.2033014</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>36.489</t>
+          <t>36489155.6960883</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>33.319</t>
+          <t>33319038.8331113</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30.596</t>
+          <t>30596120.8145369</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>28.039</t>
+          <t>28039060.9661454</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>24.451</t>
+          <t>24450563.1106419</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>23.158</t>
+          <t>23158451.1808111</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>20.516</t>
+          <t>20515715.2413289</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>17.889</t>
+          <t>17889435.2773675</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>13.841</t>
+          <t>13841362.8160748</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>11.032</t>
+          <t>11031941.2260073</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>10.524</t>
+          <t>10523594.8196973</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6.961</t>
+          <t>6961102.82277343</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>6.983</t>
+          <t>6983491.39909955</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>6.879</t>
+          <t>6878903.20686608</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6.981</t>
+          <t>6981106.89600111</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>8.075</t>
+          <t>8074971.04009227</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8.596</t>
+          <t>8596088.41727452</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>8650364.47883897</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>7.891</t>
+          <t>7890622.22862225</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>6.215</t>
+          <t>6214899.86022658</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5.675</t>
+          <t>5675074.04329671</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4500208.88140428</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4.108</t>
+          <t>4107945.76611029</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>3.311</t>
+          <t>3310736.6292159</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>3.439</t>
+          <t>3438979.82810509</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2.629</t>
+          <t>2628942.48264791</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>12.961</t>
+          <t>12961280.8137358</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11.736</t>
+          <t>11735836.4777066</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12.779</t>
+          <t>12779279.0683863</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>12.343</t>
+          <t>12342949.0390786</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>12.798</t>
+          <t>12798412.3344487</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>13.216</t>
+          <t>13215574.1011791</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12.213</t>
+          <t>12213066.9678621</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>10.348</t>
+          <t>10347570.524843</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>7.59</t>
+          <t>7589545.61564778</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>6.685</t>
+          <t>6684734.3761475</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6.038</t>
+          <t>6038449.86197199</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>5.339</t>
+          <t>5339246.64768051</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>4.147</t>
+          <t>4147404.28839189</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>3.135</t>
+          <t>3135364.63050046</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>3.454</t>
+          <t>3453682.55052492</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.991</t>
+          <t>2990843.59055704</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.877</t>
+          <t>2876620.59359795</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.119</t>
+          <t>3119087.77882992</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3.362</t>
+          <t>3362272.5725635</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3600476.19994913</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.245</t>
+          <t>4245066.92834142</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.132</t>
+          <t>4132329.21458415</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.884</t>
+          <t>3884304.73045222</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>3124985.21273185</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3.014</t>
+          <t>3014184.04300617</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2.836</t>
+          <t>2836343.49979229</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2.668</t>
+          <t>2668259.67835095</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2.245</t>
+          <t>2244581.80921816</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>1.725</t>
+          <t>1725320.04605548</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>1.817</t>
+          <t>1817096.53994002</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.039</t>
+          <t>3038896.50758701</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2.947</t>
+          <t>2946695.79957021</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.485</t>
+          <t>3485421.09275525</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3.375</t>
+          <t>3374891.49025081</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3.325</t>
+          <t>3324640.93354298</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.664</t>
+          <t>3664116.94959606</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3.814</t>
+          <t>3814249.42189278</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3.465</t>
+          <t>3464896.10537326</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2.815</t>
+          <t>2815293.17110534</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2.696</t>
+          <t>2695602.52166046</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2.458</t>
+          <t>2458230.03913119</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2.226</t>
+          <t>2225672.45453321</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>1.796</t>
+          <t>1796491.80907995</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>1.493</t>
+          <t>1492653.22853493</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>1.552</t>
+          <t>1552184.05445624</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.158</t>
+          <t>3158270.53751443</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>3.158</t>
+          <t>3157888.01354504</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.421</t>
+          <t>3420939.06362432</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3759861.17784804</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.197</t>
+          <t>4197273.94002416</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5.027</t>
+          <t>5027449.6066308</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4.858</t>
+          <t>4857655.20827285</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4.505</t>
+          <t>4505215.67932019</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>3.419</t>
+          <t>3418898.99069147</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3.232</t>
+          <t>3231896.52174735</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>3.047</t>
+          <t>3046984.86522966</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2.867</t>
+          <t>2866891.76919256</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2.379</t>
+          <t>2379140.25239491</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>1.909</t>
+          <t>1908563.42439206</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.848</t>
+          <t>1848096.03199591</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>29.371</t>
+          <t>29371288.7533477</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>23.297</t>
+          <t>23297293.6976507</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23.545</t>
+          <t>23544659.7936107</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>20.244</t>
+          <t>20243837.6034219</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>18.388</t>
+          <t>18387896.9679597</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>19.422</t>
+          <t>19421724.672467</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>18.659</t>
+          <t>18658858.9575613</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16.127</t>
+          <t>16126576.9891235</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.722</t>
+          <t>11722324.8828906</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>11.063</t>
+          <t>11062604.8896148</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>9.179</t>
+          <t>9179481.87762498</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>7.705</t>
+          <t>7704753.15922678</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>5.569</t>
+          <t>5569028.27121171</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>4.677</t>
+          <t>4676881.81947102</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>5.224</t>
+          <t>5223843.25779309</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3.615</t>
+          <t>3615400.44027569</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3.557</t>
+          <t>3556540.91763077</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3.697</t>
+          <t>3697147.76292709</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4.016</t>
+          <t>4015517.68045587</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.534</t>
+          <t>4533703.80760899</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4.866</t>
+          <t>4866411.04441611</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4.727</t>
+          <t>4726986.98714288</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4.371</t>
+          <t>4370812.44604573</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.473</t>
+          <t>3472895.24749783</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>3.194</t>
+          <t>3193512.26706024</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>3.032</t>
+          <t>3032346.89912904</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.798</t>
+          <t>2798348.27772191</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2219741.09773438</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.793</t>
+          <t>1792753.90635172</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.784</t>
+          <t>1784387.46820027</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.654</t>
+          <t>2653694.5485824</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.635</t>
+          <t>2635343.19606804</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.733</t>
+          <t>2733444.64417253</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2.897</t>
+          <t>2897286.97715092</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>3125469.18793023</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3.566</t>
+          <t>3566265.28848225</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.572</t>
+          <t>3572156.95843554</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>3.307</t>
+          <t>3306958.85226037</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2599933.69509059</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.484</t>
+          <t>2484461.13335932</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2.374</t>
+          <t>2374039.5495675</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2.208</t>
+          <t>2207621.79449968</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>1853663.20095066</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.495</t>
+          <t>1494755.3491197</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1480199.08158287</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>3.442</t>
+          <t>3441566.36476239</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.303</t>
+          <t>3303038.36810242</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3.093</t>
+          <t>3092643.4356042</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>3.183</t>
+          <t>3182519.50192044</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>3.313</t>
+          <t>3313444.15393077</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.544</t>
+          <t>3544191.75848724</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.596</t>
+          <t>3596437.71112255</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.313</t>
+          <t>3313091.98020169</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2.718</t>
+          <t>2718403.79846641</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2.495</t>
+          <t>2494919.99783032</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2.321</t>
+          <t>2321233.09729605</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2150254.82699559</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.797</t>
+          <t>1797391.36077802</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>1.602</t>
+          <t>1601927.33380724</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>1.844</t>
+          <t>1843942.16054177</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5.146</t>
+          <t>5145952.74600007</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5099838.40856576</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>5299761.38417996</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5.878</t>
+          <t>5878299.47848174</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5.895</t>
+          <t>5894977.57270036</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7.254</t>
+          <t>7253588.95545323</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6.687</t>
+          <t>6687107.08625668</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5.981</t>
+          <t>5981117.2046147</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4.384</t>
+          <t>4383934.2464101</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4.173</t>
+          <t>4172803.74802889</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>3.772</t>
+          <t>3771976.66937426</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>3.668</t>
+          <t>3667659.15862234</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.063</t>
+          <t>3062885.11686896</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.592</t>
+          <t>2591631.01471859</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.746</t>
+          <t>2745740.69687166</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>14.744</t>
+          <t>14744351.3708348</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.878</t>
+          <t>13877829.3550209</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>13.456</t>
+          <t>13455679.7103868</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>14.097</t>
+          <t>14097280.7525852</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>15.506</t>
+          <t>15505531.9208614</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>15.945</t>
+          <t>15945139.0626878</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>13.678</t>
+          <t>13677737.5309127</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11.616</t>
+          <t>11615904.9010892</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>8.679</t>
+          <t>8679388.81768541</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>7.268</t>
+          <t>7268479.77755881</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>6.612</t>
+          <t>6611879.35316846</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>6.185</t>
+          <t>6184630.40354293</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>4.953</t>
+          <t>4952746.87737877</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3540302.80160183</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4.341</t>
+          <t>4341045.12767176</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>25.699</t>
+          <t>25699271.7648833</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>23.872</t>
+          <t>23871803.0624038</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>23.255</t>
+          <t>23254848.7069684</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>62.632</t>
+          <t>62632380.2709219</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>40.701</t>
+          <t>40700670.1030267</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>35.094</t>
+          <t>35093867.3884667</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>36.316</t>
+          <t>36315745.9498601</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>32.31</t>
+          <t>32310066.505546</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>25.303</t>
+          <t>25302931.3459802</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>26880235.4068677</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>22.488</t>
+          <t>22487834.4301284</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>15.937</t>
+          <t>15936669.8579871</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>12.609</t>
+          <t>12608764.1118749</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>10.667</t>
+          <t>10667427.1467559</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>10.512</t>
+          <t>10511586.8432089</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>68.489</t>
+          <t>68489093.5025377</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>66.715</t>
+          <t>66714591.2645415</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>63.059</t>
+          <t>63059202.5048447</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>65.407</t>
+          <t>65406963.361143</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>64.899</t>
+          <t>64899296.1630036</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>69.636</t>
+          <t>69636048.3846924</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>75.152</t>
+          <t>75152484.779004</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>73.692</t>
+          <t>73692358.1846459</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>63.582</t>
+          <t>63582241.0243039</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>59.814</t>
+          <t>59814364.784713</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>50.984</t>
+          <t>50983891.8097905</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>43.827</t>
+          <t>43826895.3712811</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32999788.5005652</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>30.157</t>
+          <t>30156769.3186479</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>30.686</t>
+          <t>30686145.2219444</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.872</t>
+          <t>3872316.5426796</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.676</t>
+          <t>3675798.51012835</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3.492</t>
+          <t>3492352.34798606</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3.663</t>
+          <t>3663436.42497519</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3.896</t>
+          <t>3896437.93717443</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>4.192</t>
+          <t>4191997.99750701</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>4040196.56258587</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>3.607</t>
+          <t>3606923.59141164</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2.796</t>
+          <t>2796079.21729932</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2.702</t>
+          <t>2701921.30534326</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>2517777.29991728</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2.252</t>
+          <t>2252154.84039025</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>1.954</t>
+          <t>1954468.19226407</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1.796</t>
+          <t>1796473.37399664</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2.052</t>
+          <t>2052372.41352137</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2.874</t>
+          <t>2873903.7516294</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2669889.74430314</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.703</t>
+          <t>2702766.95238132</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2.907</t>
+          <t>2906829.86740551</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3.217</t>
+          <t>3216557.78771883</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>3729945.0716428</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.667</t>
+          <t>3667090.44026237</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>3.443</t>
+          <t>3442720.34559304</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.754</t>
+          <t>2754239.37469754</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2.631</t>
+          <t>2630839.41263981</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2.482</t>
+          <t>2482139.98157573</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2.473</t>
+          <t>2473427.04708359</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2.045</t>
+          <t>2045078.95167216</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>1.601</t>
+          <t>1601029.9686098</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>1.619</t>
+          <t>1618846.41602822</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.004</t>
+          <t>3003637.81021505</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.281</t>
+          <t>3281470.83009811</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3.534</t>
+          <t>3533968.13729337</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3.864</t>
+          <t>3863626.216336</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3.739</t>
+          <t>3738992.5680159</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3.795</t>
+          <t>3795306.46945805</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4.324</t>
+          <t>4323806.43938707</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4.362</t>
+          <t>4361868.34854323</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3.802</t>
+          <t>3802246.67045806</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3.783</t>
+          <t>3783415.59044006</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>3675264.81376283</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3.776</t>
+          <t>3775868.61542989</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>3.394</t>
+          <t>3394059.6439072</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2.924</t>
+          <t>2924074.18578843</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2.742</t>
+          <t>2741920.78990832</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10.088</t>
+          <t>10088006.3575342</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9.388</t>
+          <t>9388013.21177694</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>10.072</t>
+          <t>10071574.4466743</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>13.817</t>
+          <t>13816509.4065497</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>12.293</t>
+          <t>12292681.5004325</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12.179</t>
+          <t>12179443.8227882</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13.122</t>
+          <t>13122201.8460172</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>11.98</t>
+          <t>11979728.3467812</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>10.115</t>
+          <t>10114763.4242713</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>9.786</t>
+          <t>9786488.20435027</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7.945</t>
+          <t>7944517.07256049</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7.052</t>
+          <t>7051948.20284437</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>5.825</t>
+          <t>5824940.81042589</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>5.666</t>
+          <t>5666156.76644738</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6.288</t>
+          <t>6288225.98446796</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>34.393</t>
+          <t>34392782.3601281</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>26.955</t>
+          <t>26954934.039481</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22.442</t>
+          <t>22442039.9823294</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>21.461</t>
+          <t>21461458.896106</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>22.297</t>
+          <t>22296613.6222463</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>22.568</t>
+          <t>22567688.4105096</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>20499660.0568196</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>17.808</t>
+          <t>17807782.2309958</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>13.185</t>
+          <t>13185051.8390264</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>10.951</t>
+          <t>10951297.5117025</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>9.834</t>
+          <t>9834082.22158973</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8.378</t>
+          <t>8377748.51144106</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>6.548</t>
+          <t>6548162.66877647</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>5.32</t>
+          <t>5319500.83797555</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>6.288</t>
+          <t>6288354.42451371</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2.245</t>
+          <t>2244807.95822947</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.007</t>
+          <t>2006639.68163888</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2.057</t>
+          <t>2057083.27564429</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2.254</t>
+          <t>2253675.49494421</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2.296</t>
+          <t>2296007.7729503</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2.676</t>
+          <t>2675617.34575754</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2.499</t>
+          <t>2498542.80146907</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2.281</t>
+          <t>2280812.63182661</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.805</t>
+          <t>1804544.31665141</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.858</t>
+          <t>1858475.52143346</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.863</t>
+          <t>1862814.18720908</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.674</t>
+          <t>1674098.89792917</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>1343932.44128488</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>1140612.79688314</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.409</t>
+          <t>1409284.02908642</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>26.349</t>
+          <t>26348687.4003732</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>21.599</t>
+          <t>21598955.0302277</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>18.947</t>
+          <t>18946595.8190342</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>18.325</t>
+          <t>18325350.7062908</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>18.997</t>
+          <t>18997288.7643401</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>17.336</t>
+          <t>17336086.9760453</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>15.286</t>
+          <t>15285705.942525</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>14.575</t>
+          <t>14574891.3553231</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>10.96</t>
+          <t>10960285.3906466</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>9.874</t>
+          <t>9874110.06719694</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>8.482</t>
+          <t>8482204.53609502</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>6.873</t>
+          <t>6872703.12478397</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5.082</t>
+          <t>5082020.85457028</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4.155</t>
+          <t>4154505.80667877</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4.312</t>
+          <t>4312081.57998982</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13.258</t>
+          <t>13257908.1492435</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>11.825</t>
+          <t>11824712.6190949</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>10.151</t>
+          <t>10150832.3709998</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>10.594</t>
+          <t>10594445.7551431</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>10.118</t>
+          <t>10117617.8868713</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>9.392</t>
+          <t>9392180.41841191</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>9.174</t>
+          <t>9174074.31094579</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8.691</t>
+          <t>8690553.27702515</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>8.342</t>
+          <t>8341582.58858686</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>8.592</t>
+          <t>8592400.23685745</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>7.684</t>
+          <t>7683916.60609759</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>6.858</t>
+          <t>6857940.1007161</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>5.976</t>
+          <t>5975713.10565897</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>5.846</t>
+          <t>5845971.41537142</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>7.105</t>
+          <t>7105067.81606344</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>4.533</t>
+          <t>4533158.46039863</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4.379</t>
+          <t>4379308.02507642</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3.901</t>
+          <t>3900965.9223749</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4.012</t>
+          <t>4012397.07174443</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4.539</t>
+          <t>4538670.61582515</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5.034</t>
+          <t>5034282.0684565</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4.478</t>
+          <t>4477952.91579446</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>4.286</t>
+          <t>4285935.24463161</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3.546</t>
+          <t>3545666.13334383</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>3.335</t>
+          <t>3334622.97706303</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2.889</t>
+          <t>2888729.37490377</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3.163</t>
+          <t>3162680.42900055</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2.504</t>
+          <t>2504244.65110953</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2230407.83465025</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2.364</t>
+          <t>2363622.60430178</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>3.141</t>
+          <t>3141283.73261952</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3.225</t>
+          <t>3225097.17935749</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>3.344</t>
+          <t>3344281.82043696</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3.684</t>
+          <t>3683544.39715008</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.023</t>
+          <t>4023019.92495683</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4.241</t>
+          <t>4240821.65467716</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>4229859.88731152</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>3675400.67859586</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>3.171</t>
+          <t>3171483.10891898</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3060432.19409037</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>2.907</t>
+          <t>2906956.43208337</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2.662</t>
+          <t>2662202.00494017</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2.239</t>
+          <t>2238614.48648857</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1.871</t>
+          <t>1871008.9556734</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.944</t>
+          <t>1944139.80064114</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15.447</t>
+          <t>15446880.6821101</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>13.827</t>
+          <t>13826745.1783287</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13.766</t>
+          <t>13765521.5634694</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>13.467</t>
+          <t>13466949.7305884</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>14.281</t>
+          <t>14280576.8656169</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>14.086</t>
+          <t>14086426.2895878</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12.258</t>
+          <t>12257744.5248842</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11.115</t>
+          <t>11115262.6802646</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>9.216</t>
+          <t>9215619.59626309</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>8.314</t>
+          <t>8313930.65712939</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7.33</t>
+          <t>7330306.53741722</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6.522</t>
+          <t>6521652.36606938</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>5.177</t>
+          <t>5177460.23319773</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>3.943</t>
+          <t>3943083.33776655</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>4.781</t>
+          <t>4781195.07670137</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4.294</t>
+          <t>4293682.97561846</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.973</t>
+          <t>3973434.54762207</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>3.911</t>
+          <t>3911091.39538738</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4149881.20907847</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4.337</t>
+          <t>4336960.14130884</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5.043</t>
+          <t>5043472.55227923</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5.057</t>
+          <t>5057495.52781166</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4.588</t>
+          <t>4587753.73579828</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>3709948.23711223</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>3.516</t>
+          <t>3516218.6031372</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>3.253</t>
+          <t>3253320.89208858</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2.974</t>
+          <t>2974250.05309915</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2.543</t>
+          <t>2543353.4684079</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2.339</t>
+          <t>2338564.09108107</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2.066</t>
+          <t>2065577.05341964</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>20.772</t>
+          <t>20771893.612317</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>19.245</t>
+          <t>19245446.3713181</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>18.315</t>
+          <t>18314572.4699572</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>16.332</t>
+          <t>16331703.6918776</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18.729</t>
+          <t>18729207.0774408</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>18.411</t>
+          <t>18411331.4302549</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>16.595</t>
+          <t>16595217.4117044</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>14.834</t>
+          <t>14834241.6294062</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>11.552</t>
+          <t>11551971.1331445</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>9.156</t>
+          <t>9156157.98535625</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>7.316</t>
+          <t>7315897.73253618</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>6.241</t>
+          <t>6241074.88526663</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4499960.67982242</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>3.725</t>
+          <t>3724610.32714014</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>4.577</t>
+          <t>4577228.12316582</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>39.242</t>
+          <t>39241672.0366103</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>29889968.3234935</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>27.741</t>
+          <t>27740911.9759806</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>36.207</t>
+          <t>36207234.0335805</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>61.884</t>
+          <t>61883589.3773157</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>51.738</t>
+          <t>51737527.6883285</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>43.616</t>
+          <t>43616451.635244</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>38.052</t>
+          <t>38052294.3501356</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29479672.2851472</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>23.256</t>
+          <t>23256425.7972114</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>18.507</t>
+          <t>18506999.8686834</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>14.004</t>
+          <t>14003941.9284039</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>10.287</t>
+          <t>10287118.0624354</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>7.803</t>
+          <t>7803168.95038687</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>9.971</t>
+          <t>9970513.38147623</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>16.249</t>
+          <t>16248714.8616409</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>14.814</t>
+          <t>14814134.5488628</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13.996</t>
+          <t>13995933.8520973</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>13.607</t>
+          <t>13607323.5168187</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>15.367</t>
+          <t>15366953.5156327</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>15.273</t>
+          <t>15273055.0241169</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>14.567</t>
+          <t>14566678.6774557</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>12.055</t>
+          <t>12054692.5297717</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>8.352</t>
+          <t>8352166.53867797</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>7.666</t>
+          <t>7665952.83063126</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>7.025</t>
+          <t>7024895.40499356</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6.173</t>
+          <t>6173208.70686971</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>4.756</t>
+          <t>4755857.65147803</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>5.093</t>
+          <t>5093326.67445625</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>5.801</t>
+          <t>5800937.95299015</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7.086</t>
+          <t>7086111.34752076</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>6.781</t>
+          <t>6780919.9448006</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6.62</t>
+          <t>6620499.21850208</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>6.806</t>
+          <t>6806491.25046162</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>7.335</t>
+          <t>7335467.34246149</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8.168</t>
+          <t>8168385.33243162</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>7.877</t>
+          <t>7877381.54801187</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>7.256</t>
+          <t>7256052.81813991</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>5.938</t>
+          <t>5938457.19686427</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>5.457</t>
+          <t>5457113.1556942</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>4.992</t>
+          <t>4991948.7809827</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>4.609</t>
+          <t>4609339.7898013</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3650136.64718784</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>3.327</t>
+          <t>3327094.01841946</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>3.581</t>
+          <t>3581425.8532887</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.187</t>
+          <t>3186743.72684981</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2.794</t>
+          <t>2793829.32925733</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2.923</t>
+          <t>2923112.75416652</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>3.194</t>
+          <t>3193961.1620552</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>3.351</t>
+          <t>3351225.63845526</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3.802</t>
+          <t>3802166.92735803</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3.915</t>
+          <t>3914550.11854008</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>3.534</t>
+          <t>3533849.61248406</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2.782</t>
+          <t>2782118.74449287</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2.597</t>
+          <t>2597452.54810578</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2.493</t>
+          <t>2492691.55678056</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2.262</t>
+          <t>2261882.0220603</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>1.897</t>
+          <t>1896724.40479055</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>1.533</t>
+          <t>1532867.59652197</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>1.591</t>
+          <t>1591096.50147951</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7.142</t>
+          <t>7142410.53784243</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>6.998</t>
+          <t>6998113.09114493</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>7.063</t>
+          <t>7063206.07192702</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>7.304</t>
+          <t>7303967.69470743</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>7.932</t>
+          <t>7931850.75022103</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8.045</t>
+          <t>8045016.93576137</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10.023</t>
+          <t>10023408.9610567</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>9.335</t>
+          <t>9335101.91091829</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>7.046</t>
+          <t>7045948.68988128</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>6.124</t>
+          <t>6124206.56703902</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>5.336</t>
+          <t>5335588.43520077</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>4.933</t>
+          <t>4933177.99538946</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>3.942</t>
+          <t>3942213.14322408</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>3.265</t>
+          <t>3265361.36686173</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>3.542</t>
+          <t>3541583.82367905</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>7.614</t>
+          <t>7613858.6268195</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>7.328</t>
+          <t>7328142.9580554</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7.258</t>
+          <t>7258042.26982658</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>8.471</t>
+          <t>8471283.18402345</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>8.34</t>
+          <t>8340145.42254468</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8.719</t>
+          <t>8719015.54294514</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>9.326</t>
+          <t>9325979.35501823</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>9.565</t>
+          <t>9564755.94923525</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>8.661</t>
+          <t>8661277.44866005</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>8.732</t>
+          <t>8731597.34280213</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>7.995</t>
+          <t>7995351.55979277</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>7.589</t>
+          <t>7589199.75747241</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>6.775</t>
+          <t>6775361.28801775</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>6.202</t>
+          <t>6201548.94343791</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>6.437</t>
+          <t>6436971.44741236</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.884</t>
+          <t>3884256.26418741</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>3.649</t>
+          <t>3649362.92185701</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3510239.95634874</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>3.671</t>
+          <t>3670520.45868462</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>3.731</t>
+          <t>3731484.56313827</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>3.871</t>
+          <t>3870823.89625575</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3.764</t>
+          <t>3763634.68603124</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3.642</t>
+          <t>3641797.74107971</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>3.135</t>
+          <t>3134802.32888096</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>3.209</t>
+          <t>3209142.87404113</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>3.026</t>
+          <t>3025899.02841752</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2.838</t>
+          <t>2837967.81427779</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>2.473</t>
+          <t>2473419.25213031</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2.271</t>
+          <t>2270678.26040319</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2.251</t>
+          <t>2251436.87663757</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>23.923</t>
+          <t>23922929.524278</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>23.589</t>
+          <t>23589024.1668456</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>24.227</t>
+          <t>24226985.6023913</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>26.783</t>
+          <t>26783024.9616163</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>27600336.1915203</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>29.305</t>
+          <t>29304790.5828525</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>31.264</t>
+          <t>31263609.7556943</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>31.263</t>
+          <t>31262592.0655299</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>27.556</t>
+          <t>27555526.4787459</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>27.329</t>
+          <t>27329498.5861264</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>24.416</t>
+          <t>24416463.6455883</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>21.912</t>
+          <t>21912352.5470374</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>18.321</t>
+          <t>18320557.689006</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>15.262</t>
+          <t>15262359.8414789</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>17.175</t>
+          <t>17174513.4226201</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>529.014</t>
+          <t>529013567.340551</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>477.708</t>
+          <t>477707714.921724</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>461.676</t>
+          <t>461675903.618794</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>514.411</t>
+          <t>514410581.270484</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>531.015</t>
+          <t>531015348.225567</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>525.716</t>
+          <t>525716178.928133</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>513.178</t>
+          <t>513178456.0614</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>473.527</t>
+          <t>473527319.147364</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>384.163</t>
+          <t>384163240.545574</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>357.737</t>
+          <t>357737455.582392</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>311.973</t>
+          <t>311972701.225861</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>271.63</t>
+          <t>271629556.908915</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>215.682</t>
+          <t>215682365.160187</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>185.346</t>
+          <t>185345611.113028</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>197.934</t>
+          <t>197933860.669</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>value.m.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
